--- a/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
+++ b/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,520 +456,157 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sofia Pereira Carneiro</t>
+          <t>Camilla Silva de Sousa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>126.533.256-83</t>
+          <t>084.841.526-42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{D9986961-5490-F111-8077-00224836B90D}</t>
+          <t>{C39E55F7-A070-F111-AB0F-00224836B90D}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sofia Pereira Carneiro</t>
+          <t>Camilla Silva de Sousa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duda</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>126.533.256-83</t>
-        </is>
-      </c>
+          <t>Ajuste</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wesley Fernando pontes da costa</t>
+          <t>Iolanda Gomes da Silva</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>382.564.298-44</t>
+          <t>840.783.242-15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{8D7C5C4F-4590-F111-8077-7CED8DB11FB7}</t>
+          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wesley Fernando pontes da costa</t>
+          <t>Iolanda Gomes da Silva</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>382.564.298-44</t>
+          <t>840.783.242-15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ana Vitória de Souza e Silva</t>
+          <t>Hiago Silva de Carvalho</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>714.273.534-17</t>
+          <t>105.432.912-51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{7BFAC04B-668F-F111-8077-7CED8DB11FB7}</t>
+          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ana Vitória de Souza e Silva</t>
+          <t>Hiago Silva de Carvalho</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flávia</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>714.273.534-17</t>
+          <t>105.432.912-51</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Anna Luiza de Queiroz Sousa</t>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>088.232.583-32</t>
+          <t>440.047.368-62</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{B933DCFC-9B8E-F111-8077-000D3AC0F764}</t>
+          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anna Luiza de Queiroz Sousa</t>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flávia</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>088.232.583-32</t>
-        </is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>44004736862</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>João Vitor Barbosa da Silva</t>
+          <t>Ana julia de Souza Conceição</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>098.857.762-30</t>
+          <t>582.620.038-37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{F4A9B070-C98D-F111-8077-7CED8DB11FB7}</t>
+          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>João Vitor Barbosa da Silva</t>
+          <t>Ana julia de Souza Conceição</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flávia</t>
+          <t>Breno</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">098.857.762-30 </t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Thais Freitas Gonçalves</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>091.768.582-27</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{6E1B84D0-C48D-F111-8077-7CED8DB11FB7}</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Thais Freitas Gonçalves</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Flávia</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>091.768.582-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Fabiola Emaculada Costa de Paula</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>124.455.366-26</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{21DE753A-B88D-F111-8077-000D3AC0F764}</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Fabiola Emaculada Costa de Paula</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Flávia</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>124.455.366-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Samara da Silva Sousa</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>066.733.741-52</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{CD733715-248D-F111-8077-00224836B90D}</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Samara da Silva Sousa</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Flávia</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>066.733.741-52</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Andrei de Sena Brito</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>021.671.492-39</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{51E24E0D-218D-F111-8077-00224836B90D}</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Andrei de Sena Brito</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Thiago</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>021.671.492-39</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Aurisnei Alves Mota</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>058.004.072-07</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{E1FCC0CA-E18C-F111-8077-00224836B90D}</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Aurisnei Alves Mota</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Flávia</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>058.004.072-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Patrícia Kércia Souza da Costa</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>870.051.662-72</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{18AA023F-5F8C-F111-8077-00224836BDFB}</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Patrícia Kércia Souza da Costa</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Thiago</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>870.051.662-72</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Camilla Silva de Sousa</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>084.841.526-42</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{C39E55F7-A070-F111-AB0F-00224836B90D}</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Camilla Silva de Sousa</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Ajuste</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Iolanda Gomes da Silva</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>840.783.242-15</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Iolanda Gomes da Silva</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>840.783.242-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Hiago Silva de Carvalho</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>105.432.912-51</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Hiago Silva de Carvalho</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>105.432.912-51</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>440.047.368-62</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>44004736862</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Ana julia de Souza Conceição</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>582.620.038-37</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Ana julia de Souza Conceição</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Breno</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
         <is>
           <t>582.620.038-37</t>
         </is>

--- a/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
+++ b/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,118 +456,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Camilla Silva de Sousa</t>
+          <t>Orlandira de Carvalho Neves</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>084.841.526-42</t>
+          <t>613.983.732-49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{C39E55F7-A070-F111-AB0F-00224836B90D}</t>
+          <t>{CB35D8D2-A491-F111-8077-7CED8DB11FB7}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Camilla Silva de Sousa</t>
+          <t>Orlandira de Carvalho Neves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ajuste</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Geovana</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>613.983.732-49</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Iolanda Gomes da Silva</t>
+          <t>Nathalia Cardoso Rodrigues</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>840.783.242-15</t>
+          <t>075.696.311-70</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
+          <t>{460DEDE5-DA90-F111-8077-6045BD39BE00}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Iolanda Gomes da Silva</t>
+          <t>Nathalia Cardoso Rodrigues</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Flávia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>840.783.242-15</t>
+          <t>075.696.311-70</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hiago Silva de Carvalho</t>
+          <t>Camilla Silva de Sousa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>105.432.912-51</t>
+          <t>084.841.526-42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
+          <t>{C39E55F7-A070-F111-AB0F-00224836B90D}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hiago Silva de Carvalho</t>
+          <t>Camilla Silva de Sousa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>105.432.912-51</t>
-        </is>
-      </c>
+          <t>Ajuste</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
+          <t>Iolanda Gomes da Silva</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>440.047.368-62</t>
+          <t>840.783.242-15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
+          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
+          <t>Iolanda Gomes da Silva</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -575,38 +575,104 @@
           <t>Lorena</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>44004736862</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>840.783.242-15</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ana julia de Souza Conceição</t>
+          <t>Hiago Silva de Carvalho</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>582.620.038-37</t>
+          <t>105.432.912-51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
+          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Hiago Silva de Carvalho</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>105.432.912-51</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>440.047.368-62</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>44004736862</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Ana julia de Souza Conceição</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>582.620.038-37</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ana julia de Souza Conceição</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Breno</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>582.620.038-37</t>
         </is>

--- a/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
+++ b/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Orlandira de Carvalho Neves</t>
+          <t>Izadora Gomes dos Santos</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>613.983.732-49</t>
+          <t>032.473.102-74</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{CB35D8D2-A491-F111-8077-7CED8DB11FB7}</t>
+          <t>{6C45BD09-D891-F111-8077-00224836B90D}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Orlandira de Carvalho Neves</t>
+          <t>Izadora Gomes dos Santos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -482,92 +482,96 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>613.983.732-49</t>
+          <t>032.473.102-74</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nathalia Cardoso Rodrigues</t>
+          <t>Alexandre Lucas Farias Acácio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>075.696.311-70</t>
+          <t>037.865.912-02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{460DEDE5-DA90-F111-8077-6045BD39BE00}</t>
+          <t>{982A6835-D791-F111-8077-00224836B90D}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nathalia Cardoso Rodrigues</t>
+          <t>Alexandre Lucas Farias Acácio</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flávia</t>
+          <t>Geovana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>075.696.311-70</t>
+          <t>037.865.912-02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Camilla Silva de Sousa</t>
+          <t>Iolanda Gomes da Silva</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>084.841.526-42</t>
+          <t>840.783.242-15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{C39E55F7-A070-F111-AB0F-00224836B90D}</t>
+          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Camilla Silva de Sousa</t>
+          <t>Iolanda Gomes da Silva</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ajuste</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>840.783.242-15</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Iolanda Gomes da Silva</t>
+          <t>Hiago Silva de Carvalho</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>840.783.242-15</t>
+          <t>105.432.912-51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
+          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Iolanda Gomes da Silva</t>
+          <t>Hiago Silva de Carvalho</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -577,30 +581,30 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>840.783.242-15</t>
+          <t>105.432.912-51</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hiago Silva de Carvalho</t>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>105.432.912-51</t>
+          <t>440.047.368-62</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
+          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hiago Silva de Carvalho</t>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -608,71 +612,38 @@
           <t>Lorena</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>105.432.912-51</t>
-        </is>
+      <c r="G6" t="n">
+        <v>44004736862</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
+          <t>Ana julia de Souza Conceição</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>440.047.368-62</t>
+          <t>582.620.038-37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
+          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
+          <t>Ana julia de Souza Conceição</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>44004736862</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Ana julia de Souza Conceição</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>582.620.038-37</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Ana julia de Souza Conceição</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
           <t>Breno</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>582.620.038-37</t>
         </is>

--- a/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
+++ b/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>Nome Completo</t>
   </si>
@@ -37,18 +37,9 @@
     <t>CPF (preencher apenas com números)</t>
   </si>
   <si>
-    <t>Madson Ruan Flexa de Souza</t>
-  </si>
-  <si>
     <t>Maikon Gomes dos Santos</t>
   </si>
   <si>
-    <t>Izadora Gomes dos Santos</t>
-  </si>
-  <si>
-    <t>Alexandre Lucas Farias Acácio</t>
-  </si>
-  <si>
     <t>Iolanda Gomes da Silva</t>
   </si>
   <si>
@@ -61,18 +52,9 @@
     <t>Ana julia de Souza Conceição</t>
   </si>
   <si>
-    <t>066.776.692-89</t>
-  </si>
-  <si>
     <t>019.892.412-71</t>
   </si>
   <si>
-    <t>032.473.102-74</t>
-  </si>
-  <si>
-    <t>037.865.912-02</t>
-  </si>
-  <si>
     <t>840.783.242-15</t>
   </si>
   <si>
@@ -85,18 +67,9 @@
     <t>582.620.038-37</t>
   </si>
   <si>
-    <t>{315C91A9-8A92-F111-B8DB-7CED8DA7DB37}</t>
-  </si>
-  <si>
     <t>{55DD42FE-6992-F111-8077-6045BD39BC63}</t>
   </si>
   <si>
-    <t>{6C45BD09-D891-F111-8077-00224836B90D}</t>
-  </si>
-  <si>
-    <t>{982A6835-D791-F111-8077-00224836B90D}</t>
-  </si>
-  <si>
     <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
   </si>
   <si>
@@ -109,13 +82,7 @@
     <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
   </si>
   <si>
-    <t>Flávia</t>
-  </si>
-  <si>
     <t>Daniel</t>
-  </si>
-  <si>
-    <t>Geovana</t>
   </si>
   <si>
     <t>Lorena</t>
@@ -479,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -510,19 +477,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -530,19 +497,19 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -550,19 +517,19 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -570,19 +537,19 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="G5">
+        <v>44004736862</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -590,79 +557,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8">
-        <v>44004736862</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
+++ b/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
@@ -1,126 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
-  <si>
-    <t>Nome Completo</t>
-  </si>
-  <si>
-    <t>cpf</t>
-  </si>
-  <si>
-    <t>ID Lead</t>
-  </si>
-  <si>
-    <t>Proprietário</t>
-  </si>
-  <si>
-    <t>NOME</t>
-  </si>
-  <si>
-    <t>CONSULTOR (a)</t>
-  </si>
-  <si>
-    <t>CPF (preencher apenas com números)</t>
-  </si>
-  <si>
-    <t>Maikon Gomes dos Santos</t>
-  </si>
-  <si>
-    <t>Iolanda Gomes da Silva</t>
-  </si>
-  <si>
-    <t>Hiago Silva de Carvalho</t>
-  </si>
-  <si>
-    <t>Thayla Sthefany Da Silva Carvalho</t>
-  </si>
-  <si>
-    <t>Ana julia de Souza Conceição</t>
-  </si>
-  <si>
-    <t>019.892.412-71</t>
-  </si>
-  <si>
-    <t>840.783.242-15</t>
-  </si>
-  <si>
-    <t>105.432.912-51</t>
-  </si>
-  <si>
-    <t>440.047.368-62</t>
-  </si>
-  <si>
-    <t>582.620.038-37</t>
-  </si>
-  <si>
-    <t>{55DD42FE-6992-F111-8077-6045BD39BC63}</t>
-  </si>
-  <si>
-    <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
-  </si>
-  <si>
-    <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
-  </si>
-  <si>
-    <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
-  </si>
-  <si>
-    <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
-  </si>
-  <si>
-    <t>Daniel</t>
-  </si>
-  <si>
-    <t>Lorena</t>
-  </si>
-  <si>
-    <t>Breno</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -128,36 +42,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -445,134 +408,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5">
-        <v>44004736862</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nome Completo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>cpf</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ID Lead</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Proprietário</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>NOME</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CONSULTOR (a)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>CPF (preencher apenas com números)</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
+++ b/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,6 +450,202 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>CPF (preencher apenas com números)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Nicholas Eduardo Uchoas De Carvalho</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>426.318.258-88</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{1C376CAD-0595-F111-B8DC-00224836B90D}</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Nicholas Eduardo Uchoas De Carvalho</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Duda</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>426.318.258-88</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Maria Victória Santana Gomes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>432.518.598-46</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>{2B79CB7B-B682-F111-AB0F-7CED8DB11FB7}</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Maria Victória Santana Gomes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Duda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>432.518.598-46</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Iolanda Gomes da Silva</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>840.783.242-15</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Iolanda Gomes da Silva</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>840.783.242-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hiago Silva de Carvalho</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>105.432.912-51</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hiago Silva de Carvalho</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>105.432.912-51</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>440.047.368-62</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>44004736862</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ana julia de Souza Conceição</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>582.620.038-37</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ana julia de Souza Conceição</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Breno</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>582.620.038-37</t>
         </is>
       </c>
     </row>

--- a/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
+++ b/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,194 +456,326 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nicholas Eduardo Uchoas De Carvalho</t>
+          <t>Davidson Souza dos Santos</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>426.318.258-88</t>
+          <t>078.406.782-11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{1C376CAD-0595-F111-B8DC-00224836B90D}</t>
+          <t>{891FB7DB-C195-F111-B8DB-E4FADE034B84}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nicholas Eduardo Uchoas De Carvalho</t>
+          <t>Davidson Souza dos Santos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Geovana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>426.318.258-88</t>
+          <t>078.406.782-11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Maria Victória Santana Gomes</t>
+          <t>Josilene Gomes de Sousa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>432.518.598-46</t>
+          <t>816.734.692-72</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{2B79CB7B-B682-F111-AB0F-7CED8DB11FB7}</t>
+          <t>{1A2AA6A7-C095-F111-B8DB-70A8A5A98329}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maria Victória Santana Gomes</t>
+          <t>Josilene Gomes de Sousa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Geovana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>432.518.598-46</t>
+          <t>816.734.692-72</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Iolanda Gomes da Silva</t>
+          <t>Ruan Ferreira de Souza</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>840.783.242-15</t>
+          <t>073.985.432-12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
+          <t>{141E1E42-B395-F111-B8DB-E4FADE034B84}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Iolanda Gomes da Silva</t>
+          <t>Ruan Ferreira de Souza</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Geovana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>840.783.242-15</t>
+          <t>073.985.432-12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hiago Silva de Carvalho</t>
+          <t>Joel Maike da Silva Reis</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>105.432.912-51</t>
+          <t>019.840.442-57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
+          <t>{FD464525-B195-F111-B8DC-000D3AC0F764}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hiago Silva de Carvalho</t>
+          <t>Joel Maike da Silva Reis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Geovana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>105.432.912-51</t>
+          <t>019.840.442-57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
+          <t>Nicholas Eduardo Uchoas De Carvalho</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>440.047.368-62</t>
+          <t>426.318.258-88</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
+          <t>{1C376CAD-0595-F111-B8DC-00224836B90D}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
+          <t>Nicholas Eduardo Uchoas De Carvalho</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>44004736862</v>
+          <t>Duda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>426.318.258-88</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ana julia de Souza Conceição</t>
+          <t>Maria Victória Santana Gomes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>582.620.038-37</t>
+          <t>432.518.598-46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
+          <t>{2B79CB7B-B682-F111-AB0F-7CED8DB11FB7}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Maria Victória Santana Gomes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Duda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>432.518.598-46</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Iolanda Gomes da Silva</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>840.783.242-15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Iolanda Gomes da Silva</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>840.783.242-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Hiago Silva de Carvalho</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>105.432.912-51</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Hiago Silva de Carvalho</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>105.432.912-51</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>440.047.368-62</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>44004736862</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Ana julia de Souza Conceição</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>582.620.038-37</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ana julia de Souza Conceição</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Breno</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>582.620.038-37</t>
         </is>

--- a/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
+++ b/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,56 +456,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Davidson Souza dos Santos</t>
+          <t>Evellyn Alho Goncalves</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>078.406.782-11</t>
+          <t>047.699.132-30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{891FB7DB-C195-F111-B8DB-E4FADE034B84}</t>
+          <t>{1118DAEE-CA95-F111-B8DB-70A8A5A98329}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Davidson Souza dos Santos</t>
+          <t>Evellyn Alho Goncalves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Geovana</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>078.406.782-11</t>
+          <t>047.699.132-30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Josilene Gomes de Sousa</t>
+          <t>Ruan Ferreira de Souza</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>816.734.692-72</t>
+          <t>073.985.432-12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{1A2AA6A7-C095-F111-B8DB-70A8A5A98329}</t>
+          <t>{141E1E42-B395-F111-B8DB-E4FADE034B84}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Josilene Gomes de Sousa</t>
+          <t>Ruan Ferreira de Souza</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -515,30 +515,30 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>816.734.692-72</t>
+          <t>073.985.432-12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ruan Ferreira de Souza</t>
+          <t>Gerard Andrade de Araújo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>073.985.432-12</t>
+          <t>010.347.302-58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{141E1E42-B395-F111-B8DB-E4FADE034B84}</t>
+          <t>{00F40E56-9295-F111-B8DC-7CED8DB11FB7}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ruan Ferreira de Souza</t>
+          <t>Gerard Andrade de Araújo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -548,234 +548,135 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>073.985.432-12</t>
+          <t>010.347.302-58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Joel Maike da Silva Reis</t>
+          <t>Iolanda Gomes da Silva</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>019.840.442-57</t>
+          <t>840.783.242-15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{FD464525-B195-F111-B8DC-000D3AC0F764}</t>
+          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Joel Maike da Silva Reis</t>
+          <t>Iolanda Gomes da Silva</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Geovana</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>019.840.442-57</t>
+          <t>840.783.242-15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nicholas Eduardo Uchoas De Carvalho</t>
+          <t>Hiago Silva de Carvalho</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>426.318.258-88</t>
+          <t>105.432.912-51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{1C376CAD-0595-F111-B8DC-00224836B90D}</t>
+          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nicholas Eduardo Uchoas De Carvalho</t>
+          <t>Hiago Silva de Carvalho</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>426.318.258-88</t>
+          <t>105.432.912-51</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Maria Victória Santana Gomes</t>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>432.518.598-46</t>
+          <t>440.047.368-62</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{2B79CB7B-B682-F111-AB0F-7CED8DB11FB7}</t>
+          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maria Victória Santana Gomes</t>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duda</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>432.518.598-46</t>
-        </is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>44004736862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Iolanda Gomes da Silva</t>
+          <t>Ana julia de Souza Conceição</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>840.783.242-15</t>
+          <t>582.620.038-37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
+          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Iolanda Gomes da Silva</t>
+          <t>Ana julia de Souza Conceição</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Breno</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>840.783.242-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Hiago Silva de Carvalho</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>105.432.912-51</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Hiago Silva de Carvalho</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>105.432.912-51</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>440.047.368-62</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>44004736862</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Ana julia de Souza Conceição</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>582.620.038-37</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Ana julia de Souza Conceição</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Breno</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>582.620.038-37</t>
         </is>

--- a/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
+++ b/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,227 +456,128 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Evellyn Alho Goncalves</t>
+          <t>Iolanda Gomes da Silva</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>047.699.132-30</t>
+          <t>840.783.242-15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{1118DAEE-CA95-F111-B8DB-70A8A5A98329}</t>
+          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Evellyn Alho Goncalves</t>
+          <t>Iolanda Gomes da Silva</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>047.699.132-30</t>
+          <t>840.783.242-15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ruan Ferreira de Souza</t>
+          <t>Hiago Silva de Carvalho</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>073.985.432-12</t>
+          <t>105.432.912-51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{141E1E42-B395-F111-B8DB-E4FADE034B84}</t>
+          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ruan Ferreira de Souza</t>
+          <t>Hiago Silva de Carvalho</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geovana</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>073.985.432-12</t>
+          <t>105.432.912-51</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gerard Andrade de Araújo</t>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>010.347.302-58</t>
+          <t>440.047.368-62</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{00F40E56-9295-F111-B8DC-7CED8DB11FB7}</t>
+          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gerard Andrade de Araújo</t>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geovana</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>010.347.302-58</t>
-        </is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>44004736862</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Iolanda Gomes da Silva</t>
+          <t>Ana julia de Souza Conceição</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>840.783.242-15</t>
+          <t>582.620.038-37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
+          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Iolanda Gomes da Silva</t>
+          <t>Ana julia de Souza Conceição</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Breno</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>840.783.242-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Hiago Silva de Carvalho</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>105.432.912-51</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Hiago Silva de Carvalho</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>105.432.912-51</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>440.047.368-62</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>44004736862</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Ana julia de Souza Conceição</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>582.620.038-37</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Ana julia de Souza Conceição</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Breno</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>582.620.038-37</t>
         </is>

--- a/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
+++ b/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,128 +456,293 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Iolanda Gomes da Silva</t>
+          <t>Heitor Silva dos Santos</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>840.783.242-15</t>
+          <t>075.289.292-47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
+          <t>{19A98D0F-0E97-F111-B8DC-6045BD39BC63}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Iolanda Gomes da Silva</t>
+          <t>Heitor Silva dos Santos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Geovana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>840.783.242-15</t>
+          <t>075.289.292-47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hiago Silva de Carvalho</t>
+          <t>Ryllary Silva da Cruz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>105.432.912-51</t>
+          <t>018.021.572-80</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
+          <t>{BD136037-9196-F111-B8DC-00224836B90D}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hiago Silva de Carvalho</t>
+          <t>Ryllary Silva da Cruz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Geovana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>105.432.912-51</t>
+          <t>018.021.572-80</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
+          <t>Alessandra Augusta Leandro da Silva</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>440.047.368-62</t>
+          <t>277.755.558-31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
+          <t>{5EE9AF39-8796-F111-B8DC-00224836B90D}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
+          <t>Alessandra Augusta Leandro da Silva</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>44004736862</v>
+          <t>Hailton</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>277.755.558-31</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ana julia de Souza Conceição</t>
+          <t>Thamyris Biancardi Schueroff</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>582.620.038-37</t>
+          <t>025.480.562-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
+          <t>{7DCCA1AA-8096-F111-B8DC-000D3AC0F764}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Thamyris Biancardi Schueroff</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Geovana</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>025.480.562-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ana Luiza Souza de Paula</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>522.709.538-86</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{1FE894D3-4D96-F111-B8DC-00224836B90D}</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ana Luiza Souza de Paula</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Adauri</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>522.709.538-86</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Iolanda Gomes da Silva</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>840.783.242-15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Iolanda Gomes da Silva</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>840.783.242-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hiago Silva de Carvalho</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>105.432.912-51</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hiago Silva de Carvalho</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>105.432.912-51</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>440.047.368-62</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Thayla Sthefany Da Silva Carvalho</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>44004736862</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Ana julia de Souza Conceição</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>582.620.038-37</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ana julia de Souza Conceição</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Breno</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>582.620.038-37</t>
         </is>

--- a/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
+++ b/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,229 +522,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alessandra Augusta Leandro da Silva</t>
+          <t>Thamyris Biancardi Schueroff</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>277.755.558-31</t>
+          <t>025.480.562-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{5EE9AF39-8796-F111-B8DC-00224836B90D}</t>
+          <t>{7DCCA1AA-8096-F111-B8DC-000D3AC0F764}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alessandra Augusta Leandro da Silva</t>
+          <t>Thamyris Biancardi Schueroff</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hailton</t>
+          <t>Geovana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>277.755.558-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thamyris Biancardi Schueroff</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>025.480.562-01</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>{7DCCA1AA-8096-F111-B8DC-000D3AC0F764}</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Thamyris Biancardi Schueroff</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Geovana</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>025.480.562-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ana Luiza Souza de Paula</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>522.709.538-86</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{1FE894D3-4D96-F111-B8DC-00224836B90D}</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ana Luiza Souza de Paula</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Adauri</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>522.709.538-86</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Iolanda Gomes da Silva</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>840.783.242-15</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{CF70C4D2-DB6F-F111-AB0E-6045BD39BC63}</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Iolanda Gomes da Silva</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>840.783.242-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Hiago Silva de Carvalho</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>105.432.912-51</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{F84B8AA5-644D-F111-BEC7-000D3A8928F0}</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Hiago Silva de Carvalho</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>105.432.912-51</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>440.047.368-62</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{58217A10-404D-F111-BEC7-7CED8DA8AD31}</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Thayla Sthefany Da Silva Carvalho</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Lorena</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>44004736862</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Ana julia de Souza Conceição</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>582.620.038-37</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{4506AB90-8349-F111-BEC7-7CED8DA8AD31}</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Ana julia de Souza Conceição</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Breno</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>582.620.038-37</t>
         </is>
       </c>
     </row>

--- a/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
+++ b/leads_sem_proprietario/matriculas_sem_proprietario.xlsx
@@ -1,40 +1,441 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="130">
+  <si>
+    <t>Nome Completo_x</t>
+  </si>
+  <si>
+    <t>cpf</t>
+  </si>
+  <si>
+    <t>ID Lead</t>
+  </si>
+  <si>
+    <t>Proprietário</t>
+  </si>
+  <si>
+    <t>NOME</t>
+  </si>
+  <si>
+    <t>CONSULTOR (a)</t>
+  </si>
+  <si>
+    <t>CPF (preencher apenas com números)</t>
+  </si>
+  <si>
+    <t>Isabela Victoria Ribeiro Cirqueira</t>
+  </si>
+  <si>
+    <t>Heitor Silva dos Santos</t>
+  </si>
+  <si>
+    <t>Ryllary Silva da Cruz</t>
+  </si>
+  <si>
+    <t>Thamyris Biancardi Schueroff</t>
+  </si>
+  <si>
+    <t>Luana Pessoa Assunção Silva</t>
+  </si>
+  <si>
+    <t>Natassya Rafaela Conceição de Sousa</t>
+  </si>
+  <si>
+    <t>Rafaela da Silva Sousa Curvina</t>
+  </si>
+  <si>
+    <t>Viviane Lima da Silva Nascimento</t>
+  </si>
+  <si>
+    <t>Maria Paula de Toledo</t>
+  </si>
+  <si>
+    <t>João Victor Cruz Tomaela</t>
+  </si>
+  <si>
+    <t>Anne Mayara Oliveira Batista</t>
+  </si>
+  <si>
+    <t>Joicellen Rosa da Costa</t>
+  </si>
+  <si>
+    <t>Pedro Neto Sousa de Jesus</t>
+  </si>
+  <si>
+    <t>Silvano Santos da Gama</t>
+  </si>
+  <si>
+    <t>Jason Pinho do Nascimento</t>
+  </si>
+  <si>
+    <t>Amanda Leticia dos Santos Pereira</t>
+  </si>
+  <si>
+    <t>Ana Lourdes Torres da Silva</t>
+  </si>
+  <si>
+    <t>Eduarda Santos</t>
+  </si>
+  <si>
+    <t>Ariana Flavia Lucio Geronimo Lucio de Azevedo</t>
+  </si>
+  <si>
+    <t>Camilla Silva de Sousa</t>
+  </si>
+  <si>
+    <t>Ana Flavia dos Santos Herculano</t>
+  </si>
+  <si>
+    <t>Marcela dos Santos Oliveira Grassi</t>
+  </si>
+  <si>
+    <t>Rodrigo da Silva Aguiar</t>
+  </si>
+  <si>
+    <t>Jhennifer Rayssa Sales da Luz</t>
+  </si>
+  <si>
+    <t>Larissa Correia dos Santos</t>
+  </si>
+  <si>
+    <t>Carleane Leite Veloso</t>
+  </si>
+  <si>
+    <t>Juliana Almeida Araujo</t>
+  </si>
+  <si>
+    <t>Ana Sara Noivo Ramos</t>
+  </si>
+  <si>
+    <t>711.050.201-50</t>
+  </si>
+  <si>
+    <t>075.289.292-47</t>
+  </si>
+  <si>
+    <t>018.021.572-80</t>
+  </si>
+  <si>
+    <t>025.480.562-01</t>
+  </si>
+  <si>
+    <t>030.440.202-80</t>
+  </si>
+  <si>
+    <t>118.153.623-59</t>
+  </si>
+  <si>
+    <t>547.612.122-68</t>
+  </si>
+  <si>
+    <t>002.282.892-38</t>
+  </si>
+  <si>
+    <t>550.944.478-90</t>
+  </si>
+  <si>
+    <t>060.554.832-38</t>
+  </si>
+  <si>
+    <t>010.963.102-10</t>
+  </si>
+  <si>
+    <t>077.741.862-20</t>
+  </si>
+  <si>
+    <t>071.801.932-67</t>
+  </si>
+  <si>
+    <t>009.532.482-83</t>
+  </si>
+  <si>
+    <t>017.405.852-75</t>
+  </si>
+  <si>
+    <t>039.018.732-10</t>
+  </si>
+  <si>
+    <t>064.762.482-60</t>
+  </si>
+  <si>
+    <t>088.055.412-65</t>
+  </si>
+  <si>
+    <t>392.271.258-41</t>
+  </si>
+  <si>
+    <t>084.841.526-42</t>
+  </si>
+  <si>
+    <t>158.652.657-09</t>
+  </si>
+  <si>
+    <t>476.028.548-29</t>
+  </si>
+  <si>
+    <t>226.452.788-92</t>
+  </si>
+  <si>
+    <t>068.703.402-77</t>
+  </si>
+  <si>
+    <t>524.281.218-47</t>
+  </si>
+  <si>
+    <t>104.323.202-88</t>
+  </si>
+  <si>
+    <t>607.823.828-00</t>
+  </si>
+  <si>
+    <t>499.232.198-44</t>
+  </si>
+  <si>
+    <t>{5C53F411-F370-F111-AB0F-00224836BDFB}</t>
+  </si>
+  <si>
+    <t>{19A98D0F-0E97-F111-B8DC-6045BD39BC63}</t>
+  </si>
+  <si>
+    <t>{BD136037-9196-F111-B8DC-00224836B90D}</t>
+  </si>
+  <si>
+    <t>{7DCCA1AA-8096-F111-B8DC-000D3AC0F764}</t>
+  </si>
+  <si>
+    <t>{E252919B-3793-F111-B8DC-000D3AC0F764}</t>
+  </si>
+  <si>
+    <t>{4648C312-4675-F111-AB0E-000D3AC0F764}</t>
+  </si>
+  <si>
+    <t>{5E513D8F-A891-F111-8077-6045BD39BC63}</t>
+  </si>
+  <si>
+    <t>{8F0969C0-9B91-F111-8076-6045BD38FB26}</t>
+  </si>
+  <si>
+    <t>{FCA3CE06-D590-F111-8077-000D3AC0F764}</t>
+  </si>
+  <si>
+    <t>{0E0D932D-3A90-F111-8077-6045BD39BE00}</t>
+  </si>
+  <si>
+    <t>{38609495-6D8F-F111-8077-6045BD39BC63}</t>
+  </si>
+  <si>
+    <t>{4A8BCC8D-ED89-F111-8077-000D3AC0F764}</t>
+  </si>
+  <si>
+    <t>{A72A9882-8E86-F111-AB0F-6045BD39BC63}</t>
+  </si>
+  <si>
+    <t>{A729FA23-4081-F111-AB0E-6045BD39BE00}</t>
+  </si>
+  <si>
+    <t>{2B61517C-2681-F111-AB0E-6045BD39BE00}</t>
+  </si>
+  <si>
+    <t>{9BC3EEC1-2581-F111-AB0E-6045BD39BE00}</t>
+  </si>
+  <si>
+    <t>{0778B024-CB5F-F111-A826-7CED8DA8D832}</t>
+  </si>
+  <si>
+    <t>{49CF69B9-BA65-F111-AB0C-6045BD39BC63}</t>
+  </si>
+  <si>
+    <t>{664A4113-8974-F111-AB0E-7CED8DB11FB7}</t>
+  </si>
+  <si>
+    <t>{C39E55F7-A070-F111-AB0F-00224836B90D}</t>
+  </si>
+  <si>
+    <t>{B31072D7-9E66-F111-AB0C-000D3AC0F764}</t>
+  </si>
+  <si>
+    <t>{7FDFA126-B65B-F111-A825-7CED8DA8D832}</t>
+  </si>
+  <si>
+    <t>{D3D7D84F-8B58-F111-A825-7CED8DA8D832}</t>
+  </si>
+  <si>
+    <t>{E2DC51BD-674D-F111-BEC7-7CED8DA8AD31}</t>
+  </si>
+  <si>
+    <t>{3F7D194F-664D-F111-BEC7-00224836CC3A}</t>
+  </si>
+  <si>
+    <t>{59A1EBB9-624D-F111-BEC7-000D3A8928F0}</t>
+  </si>
+  <si>
+    <t>{2DAD07FF-614D-F111-BEC7-7CED8DA8AD31}</t>
+  </si>
+  <si>
+    <t>{05BFE302-0F4B-F111-BEC7-7CED8DA8AD31}</t>
+  </si>
+  <si>
+    <t>Pamela Alves da silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Luana Pessoa Assunção Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Natassya Rafaela Conceição de Sousa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rafaela da Silva Sousa Curvina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viviane Lima da Silva Nascimento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Paula de Toledo </t>
+  </si>
+  <si>
+    <t>Victor Cruz Tomaela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mayara Oliveira Batista </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joicellen rosa da Costa </t>
+  </si>
+  <si>
+    <t>Pedro neto Sousa de Jesus</t>
+  </si>
+  <si>
+    <t>Silvano santos da gama</t>
+  </si>
+  <si>
+    <t>Jason pinho do Nascimento</t>
+  </si>
+  <si>
+    <t>Amanda Leticia Dos Santos Pereira</t>
+  </si>
+  <si>
+    <t>Ana lourdes Torres da Silva</t>
+  </si>
+  <si>
+    <t>Eduarda Moraes dos Santos</t>
+  </si>
+  <si>
+    <t>Ariana Flavia Lucio Gerônimo de Azevedo</t>
+  </si>
+  <si>
+    <t>Ana Flávia dos Santos Herculano</t>
+  </si>
+  <si>
+    <t>Marcela Dos Santos Oliveira Grassi</t>
+  </si>
+  <si>
+    <t>Rodrigo da SIlva Aguiar</t>
+  </si>
+  <si>
+    <t>JHENNIFER RAYSSA SALES DA LUZ</t>
+  </si>
+  <si>
+    <t>LARISSA CORREIA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>CARLEANE LEITE VELOSO</t>
+  </si>
+  <si>
+    <t>JULIANA ALMEIDA ARAUJO</t>
+  </si>
+  <si>
+    <t>Ana Sara noivo Ramos</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>Geovana</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Flávia</t>
+  </si>
+  <si>
+    <t>Agnata</t>
+  </si>
+  <si>
+    <t>Thiago</t>
+  </si>
+  <si>
+    <t>Hailton</t>
+  </si>
+  <si>
+    <t>Ajuste</t>
+  </si>
+  <si>
+    <t>Thalia</t>
+  </si>
+  <si>
+    <t>Adauri</t>
+  </si>
+  <si>
+    <t>Karolaine</t>
+  </si>
+  <si>
+    <t>711.05.02.01-50</t>
+  </si>
+  <si>
+    <t>032.812.862-75</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 030.440.202.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">002.282.892-38 </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +443,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,151 +760,602 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nome Completo</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>cpf</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ID Lead</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Proprietário</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>NOME</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>CONSULTOR (a)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>CPF (preencher apenas com números)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Heitor Silva dos Santos</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>075.289.292-47</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>{19A98D0F-0E97-F111-B8DC-6045BD39BC63}</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Heitor Silva dos Santos</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Geovana</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>075.289.292-47</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ryllary Silva da Cruz</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>018.021.572-80</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>{BD136037-9196-F111-B8DC-00224836B90D}</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Ryllary Silva da Cruz</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Geovana</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>018.021.572-80</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Thamyris Biancardi Schueroff</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>025.480.562-01</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>{7DCCA1AA-8096-F111-B8DC-000D3AC0F764}</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Thamyris Biancardi Schueroff</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Geovana</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>025.480.562-01</t>
-        </is>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="E6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" t="s">
+        <v>116</v>
+      </c>
+      <c r="G10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11">
+        <v>55094447890</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" t="s">
+        <v>116</v>
+      </c>
+      <c r="G14">
+        <v>7774186220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" t="s">
+        <v>121</v>
+      </c>
+      <c r="G21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25">
+        <v>22645278892</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" t="s">
+        <v>124</v>
+      </c>
+      <c r="G27">
+        <v>52428121847</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" t="s">
+        <v>112</v>
+      </c>
+      <c r="F28" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28">
+        <v>10432320288</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29">
+        <v>6078238280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>